--- a/data/trans_orig/P35A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P35A_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que siga una alimentación saludable en 2023</t>
+          <t>Población según si su médico le ha aconsejado que siga una alimentación saludable en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29740</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53944</t>
+          <t>55312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28661</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48529</t>
+          <t>48135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65229</t>
+          <t>63253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95589</t>
+          <t>95248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>139653</t>
+          <t>139055</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>186598</t>
+          <t>184998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>161650</t>
+          <t>161001</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>198352</t>
+          <t>195448</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>307454</t>
+          <t>311173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>366982</t>
+          <t>369093</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>398133</t>
+          <t>398072</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>445142</t>
+          <t>446811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>425573</t>
+          <t>428516</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>467474</t>
+          <t>466929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>839173</t>
+          <t>840858</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>903086</t>
+          <t>901432</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44287</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116692</t>
+          <t>119904</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84983</t>
+          <t>84924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>118885</t>
+          <t>117004</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>128390</t>
+          <t>122141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>220515</t>
+          <t>220641</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>48117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31215</t>
+          <t>31767</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51845</t>
+          <t>51819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49216</t>
+          <t>50368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92343</t>
+          <t>92465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271895</t>
+          <t>270770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>793771</t>
+          <t>835644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231717</t>
+          <t>230142</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>280327</t>
+          <t>276275</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>531626</t>
+          <t>525503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1182585</t>
+          <t>1185592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>338295</t>
+          <t>298797</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>772729</t>
+          <t>775623</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>537539</t>
+          <t>538614</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>588836</t>
+          <t>590954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>784339</t>
+          <t>776766</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1330355</t>
+          <t>1334311</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,03%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63088</t>
+          <t>62463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105171</t>
+          <t>104475</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25672</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72138</t>
+          <t>73747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88531</t>
+          <t>89918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167180</t>
+          <t>162278</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31442</t>
+          <t>30998</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29649</t>
+          <t>29444</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22384</t>
+          <t>23402</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>53141</t>
+          <t>51633</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131930</t>
+          <t>136336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180303</t>
+          <t>182400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91570</t>
+          <t>87625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>236300</t>
+          <t>232307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>215461</t>
+          <t>221147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>389964</t>
+          <t>393066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418711</t>
+          <t>418166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475627</t>
+          <t>473933</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>605792</t>
+          <t>610679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>806588</t>
+          <t>814323</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1048210</t>
+          <t>1050358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1310545</t>
+          <t>1290220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36757</t>
+          <t>37723</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64328</t>
+          <t>66096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30894</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>54425</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74920</t>
+          <t>73596</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111752</t>
+          <t>109896</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33004</t>
+          <t>34145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21321</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>40172</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42801</t>
+          <t>42124</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68686</t>
+          <t>68601</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>209086</t>
+          <t>211215</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>263649</t>
+          <t>262521</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>209607</t>
+          <t>209381</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>287862</t>
+          <t>289633</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>440183</t>
+          <t>428068</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>541826</t>
+          <t>535452</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>587395</t>
+          <t>586716</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>647942</t>
+          <t>643741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>730354</t>
+          <t>728784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>826126</t>
+          <t>825920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1330182</t>
+          <t>1333537</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1451110</t>
+          <t>1458575</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,14%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>203570</t>
+          <t>201115</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>299651</t>
+          <t>299922</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>187843</t>
+          <t>188587</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>261118</t>
+          <t>263072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>429352</t>
+          <t>423486</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>542449</t>
+          <t>545458</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107807</t>
+          <t>108413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79958</t>
+          <t>77182</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119839</t>
+          <t>118295</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158291</t>
+          <t>155921</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218508</t>
+          <t>215692</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>821124</t>
+          <t>818537</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1538492</t>
+          <t>1552499</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>679621</t>
+          <t>703501</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>939244</t>
+          <t>950087</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1657581</t>
+          <t>1654042</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2547449</t>
+          <t>2478535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1659202</t>
+          <t>1639125</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2273100</t>
+          <t>2275089</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2366842</t>
+          <t>2358953</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2703283</t>
+          <t>2699288</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4068758</t>
+          <t>4031073</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4795479</t>
+          <t>4786999</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P35A_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41338</t>
+          <t>46586</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>34335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55312</t>
+          <t>63807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37266</t>
+          <t>41181</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29035</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48135</t>
+          <t>52963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>78604</t>
+          <t>87766</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63253</t>
+          <t>71834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95248</t>
+          <t>107147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18202</t>
+          <t>20999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>25027</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32339</t>
+          <t>35912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>160861</t>
+          <t>170798</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>139055</t>
+          <t>147484</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>184998</t>
+          <t>193707</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>177662</t>
+          <t>193440</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>161001</t>
+          <t>175349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>195448</t>
+          <t>214559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>338522</t>
+          <t>364238</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>311173</t>
+          <t>332321</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>369093</t>
+          <t>393970</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>422202</t>
+          <t>460851</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>398072</t>
+          <t>434717</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>446811</t>
+          <t>484457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>448438</t>
+          <t>485141</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>428516</t>
+          <t>462721</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>466929</t>
+          <t>504494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>870641</t>
+          <t>945991</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>840858</t>
+          <t>915723</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>901432</t>
+          <t>982852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>674966</t>
+          <t>732313</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674966</t>
+          <t>732313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674966</t>
+          <t>732313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1310407</t>
+          <t>1423022</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1310407</t>
+          <t>1423022</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1310407</t>
+          <t>1423022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85751</t>
+          <t>95972</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41960</t>
+          <t>77222</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119904</t>
+          <t>119585</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>99606</t>
+          <t>110501</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84924</t>
+          <t>93005</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117004</t>
+          <t>129749</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>185357</t>
+          <t>206473</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>122141</t>
+          <t>182000</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>220641</t>
+          <t>234213</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>38305</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>26862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48117</t>
+          <t>53100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40772</t>
+          <t>47499</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>36676</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51819</t>
+          <t>59400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73929</t>
+          <t>85804</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50368</t>
+          <t>68014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92465</t>
+          <t>106207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>468856</t>
+          <t>254157</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270770</t>
+          <t>226689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>835644</t>
+          <t>285786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>254691</t>
+          <t>284252</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>230142</t>
+          <t>259571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276275</t>
+          <t>309059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>723547</t>
+          <t>538409</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525503</t>
+          <t>503525</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1185592</t>
+          <t>580054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>605100</t>
+          <t>660482</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>298797</t>
+          <t>625133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>775623</t>
+          <t>696124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>563038</t>
+          <t>628586</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>538614</t>
+          <t>600575</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>590954</t>
+          <t>657153</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1168138</t>
+          <t>1289069</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>776766</t>
+          <t>1242158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1334311</t>
+          <t>1333760</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,92%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>81778</t>
+          <t>91899</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62463</t>
+          <t>70316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104475</t>
+          <t>116262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50958</t>
+          <t>64322</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>49419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73747</t>
+          <t>82963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>132736</t>
+          <t>156221</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>89918</t>
+          <t>129338</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162278</t>
+          <t>184523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>10414</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30998</t>
+          <t>30956</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29444</t>
+          <t>29061</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>36617</t>
+          <t>39358</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>28702</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>51633</t>
+          <t>54528</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>157398</t>
+          <t>175655</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136336</t>
+          <t>153309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>182400</t>
+          <t>203407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>173800</t>
+          <t>202651</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87625</t>
+          <t>181859</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232307</t>
+          <t>225532</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>331197</t>
+          <t>378305</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>221147</t>
+          <t>344773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393066</t>
+          <t>413736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>447311</t>
+          <t>516131</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418166</t>
+          <t>484002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473933</t>
+          <t>545928</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>689618</t>
+          <t>524720</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>610679</t>
+          <t>499122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>814323</t>
+          <t>549867</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1136929</t>
+          <t>1040851</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1050358</t>
+          <t>1001911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1290220</t>
+          <t>1082918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50136</t>
+          <t>63163</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37723</t>
+          <t>47931</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66096</t>
+          <t>80151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>51229</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54425</t>
+          <t>65027</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>91494</t>
+          <t>114392</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73596</t>
+          <t>92359</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109896</t>
+          <t>138284</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23987</t>
+          <t>28399</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16333</t>
+          <t>19243</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34145</t>
+          <t>40118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>34294</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>25759</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40172</t>
+          <t>46761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>53878</t>
+          <t>62693</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42124</t>
+          <t>50385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68601</t>
+          <t>79168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>236123</t>
+          <t>245927</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>211215</t>
+          <t>219064</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>262521</t>
+          <t>271507</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>259588</t>
+          <t>281528</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>209381</t>
+          <t>257955</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>289633</t>
+          <t>307228</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>495710</t>
+          <t>527456</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>428068</t>
+          <t>490242</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>535452</t>
+          <t>562062</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>616586</t>
+          <t>652573</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>586716</t>
+          <t>622838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>643741</t>
+          <t>682299</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>764094</t>
+          <t>751989</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>728784</t>
+          <t>723340</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>825920</t>
+          <t>777961</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1380680</t>
+          <t>1404563</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1333537</t>
+          <t>1363507</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1458575</t>
+          <t>1446528</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>259003</t>
+          <t>297620</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>201115</t>
+          <t>260999</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>299922</t>
+          <t>336109</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>229188</t>
+          <t>267232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>188587</t>
+          <t>238931</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>263072</t>
+          <t>301507</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>488192</t>
+          <t>564853</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>423486</t>
+          <t>519408</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>545458</t>
+          <t>613316</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>86377</t>
+          <t>98568</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64626</t>
+          <t>78419</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108413</t>
+          <t>120532</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>114314</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77182</t>
+          <t>97839</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118295</t>
+          <t>134168</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>187064</t>
+          <t>212882</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>155921</t>
+          <t>186122</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>215692</t>
+          <t>239922</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1023237</t>
+          <t>846536</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>818537</t>
+          <t>796297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1552499</t>
+          <t>906403</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>865740</t>
+          <t>961872</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>703501</t>
+          <t>917302</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>950087</t>
+          <t>1008674</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1888977</t>
+          <t>1808408</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1654042</t>
+          <t>1736253</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2478535</t>
+          <t>1882787</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2091200</t>
+          <t>2290037</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1639125</t>
+          <t>2224767</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2275089</t>
+          <t>2348590</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2465189</t>
+          <t>2390437</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2358953</t>
+          <t>2335252</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2699288</t>
+          <t>2437888</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4556388</t>
+          <t>4680474</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4031073</t>
+          <t>4599983</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4786999</t>
+          <t>4760746</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3660804</t>
+          <t>3733855</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3660804</t>
+          <t>3733855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3660804</t>
+          <t>3733855</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7120621</t>
+          <t>7266617</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7120621</t>
+          <t>7266617</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7120621</t>
+          <t>7266617</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
